--- a/output/pdf_financials_xlsx/BKI.xlsx
+++ b/output/pdf_financials_xlsx/BKI.xlsx
@@ -1168,13 +1168,13 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.907483</v>
+        <v>-2.907483</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.124529</v>
+        <v>-2.124529</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.898038</v>
+        <v>-2.898038</v>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.130978</v>
+        <v>-2.130978</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.452504</v>
+        <v>-1.452504</v>
       </c>
     </row>
     <row r="17">
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.907483</v>
+        <v>-2.907483</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.124529</v>
+        <v>-2.124529</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.898038</v>
+        <v>-2.898038</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.130978</v>
+        <v>-2.130978</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.452504</v>
+        <v>-1.452504</v>
       </c>
     </row>
     <row r="21">
@@ -1546,13 +1546,13 @@
         <v>-1.747364</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.907483</v>
+        <v>-2.907483</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.124529</v>
+        <v>-2.124529</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.898038</v>
+        <v>-2.898038</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-5.827489</v>
@@ -1564,10 +1564,10 @@
         <v>-1.580905</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2.130978</v>
+        <v>-2.130978</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.452504</v>
+        <v>-1.452504</v>
       </c>
     </row>
     <row r="24">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-145.37415</v>
+        <v>145.37415</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-144.9019</v>
+        <v>144.9019</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1754,13 +1754,13 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.907483</v>
+        <v>-2.907483</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.124529</v>
+        <v>-2.124529</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.898038</v>
+        <v>-2.898038</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.130978</v>
+        <v>-2.130978</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.452504</v>
+        <v>-1.452504</v>
       </c>
     </row>
     <row r="28">
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.913951</v>
+        <v>-2.901015</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.13713</v>
+        <v>-2.111928</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.90215</v>
+        <v>-2.893926</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.13382</v>
+        <v>-2.128136</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.565633</v>
+        <v>-1.339375</v>
       </c>
     </row>
     <row r="30">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4462,25 +4462,25 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.750184</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.5518110000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.965701</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.970044</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.290804</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.609624</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.04807</v>
       </c>
     </row>
     <row r="93">
@@ -7073,7 +7073,11 @@
           <t>Share based payments reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -7753,7 +7757,11 @@
           <t>Warrant reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -8094,7 +8102,11 @@
           <t>Share based payments reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -8163,7 +8175,11 @@
           <t>Warrant reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -8642,7 +8658,11 @@
           <t>Share based payments reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -8711,7 +8731,11 @@
           <t>Warrant reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -9695,7 +9719,11 @@
           <t>Share based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -9764,7 +9792,11 @@
           <t>Warrant reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -19277,13 +19309,13 @@
         <v>1.747364</v>
       </c>
       <c r="H191" s="5" t="n">
-        <v>2.907483</v>
+        <v>-2.907483</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>2.124529</v>
+        <v>-2.124529</v>
       </c>
       <c r="J191" s="5" t="n">
-        <v>2.898038</v>
+        <v>-2.898038</v>
       </c>
       <c r="K191" s="5" t="n">
         <v>5.827489</v>
@@ -19295,10 +19327,10 @@
         <v>1.580905</v>
       </c>
       <c r="N191" s="5" t="n">
-        <v>2.130978</v>
+        <v>-2.130978</v>
       </c>
       <c r="O191" s="5" t="n">
-        <v>1.452504</v>
+        <v>-1.452504</v>
       </c>
     </row>
     <row r="192">
@@ -19464,13 +19496,13 @@
         </is>
       </c>
       <c r="H194" s="5" t="n">
-        <v>1.575236</v>
+        <v>-1.575236</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>3.58143</v>
+        <v>-3.58143</v>
       </c>
       <c r="J194" s="5" t="n">
-        <v>3.066005</v>
+        <v>-3.066005</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -19484,10 +19516,10 @@
         <v>1.578135</v>
       </c>
       <c r="N194" s="5" t="n">
-        <v>2.042712</v>
+        <v>-2.042712</v>
       </c>
       <c r="O194" s="5" t="n">
-        <v>1.561295</v>
+        <v>-1.561295</v>
       </c>
     </row>
     <row r="195">

--- a/output/pdf_financials_xlsx/BKI.xlsx
+++ b/output/pdf_financials_xlsx/BKI.xlsx
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001645</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005910000000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003681</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.048546</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.033779</v>
       </c>
     </row>
     <row r="13">
@@ -1754,13 +1754,13 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.907483</v>
+        <v>-2.905838</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.124529</v>
+        <v>-2.123938</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.898038</v>
+        <v>-2.894357</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.130978</v>
+        <v>-2.082432</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.452504</v>
+        <v>-1.418725</v>
       </c>
     </row>
     <row r="28">
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.901015</v>
+        <v>-2.89937</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.111928</v>
+        <v>-2.111337</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.893926</v>
+        <v>-2.890245</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.128136</v>
+        <v>-2.07959</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.339375</v>
+        <v>-1.305596</v>
       </c>
     </row>
     <row r="30">
@@ -2084,19 +2084,19 @@
         <v>14.054345</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.244395</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.838278</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.112205</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.9888439999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>5.694803</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.263511</v>
@@ -2164,19 +2164,19 @@
         <v>14.054345</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.244395</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.838278</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.112205</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.9888439999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>5.694803</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>2.263511</v>
@@ -2644,19 +2644,19 @@
         <v>0.005282</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.544971</v>
+        <v>2.300576</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.191433</v>
+        <v>3.353155</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.6738499999999999</v>
+        <v>0.5616449999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.091485</v>
+        <v>0.102641</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.386893</v>
+        <v>0.69209</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.06471399999999999</v>
@@ -5724,10 +5724,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.011821</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.141847</v>
       </c>
     </row>
     <row r="125">
@@ -5764,10 +5764,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.011821</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.141847</v>
       </c>
     </row>
     <row r="126">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -12487,7 +12487,11 @@
           <t>Lease payments (Note 12)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -13214,7 +13218,11 @@
           <t>Lease payments (Note 16)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -19164,7 +19172,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -19237,7 +19245,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">

--- a/output/pdf_financials_xlsx/BKI.xlsx
+++ b/output/pdf_financials_xlsx/BKI.xlsx
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.120578</v>
+        <v>1.413623</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.055463</v>
+        <v>1.232145</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.903115</v>
+        <v>1.057642</v>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.418667</v>
+        <v>0.589983</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.413483</v>
+        <v>0.519997</v>
       </c>
     </row>
     <row r="8">
@@ -856,13 +856,13 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.120578</v>
+        <v>1.413623</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.055463</v>
+        <v>1.232145</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.903115</v>
+        <v>1.057642</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.418667</v>
+        <v>0.589983</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.413483</v>
+        <v>0.519997</v>
       </c>
     </row>
     <row r="11">
@@ -908,13 +908,13 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-1.120578</v>
+        <v>-1.413623</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.055463</v>
+        <v>-1.232145</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.903115</v>
+        <v>-1.057642</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.418667</v>
+        <v>-0.589983</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.413483</v>
+        <v>-0.519997</v>
       </c>
     </row>
     <row r="12">
@@ -5152,10 +5152,10 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.053455</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.005458</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -5177,28 +5177,28 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004086</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003501</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01197</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005156</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005395</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004437</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005993</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000145</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.035967</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.003768</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -6119,28 +6119,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004086</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003501</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01197</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005156</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005395</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004437</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005993</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000145</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -6159,28 +6159,28 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-6.551159</v>
+        <v>-6.555245</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.55445</v>
+        <v>-2.557951</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.975421</v>
+        <v>-1.987391</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.523077</v>
+        <v>-2.528233</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.929487</v>
+        <v>-1.934882</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-2.230027</v>
+        <v>-2.234464</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-4.95655</v>
+        <v>-4.962543</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-3.279065</v>
+        <v>-3.27921</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-1.216535</v>
@@ -13630,7 +13630,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -13760,7 +13764,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -13973,7 +13981,11 @@
           <t>Private placement (Note 7 and Note 9)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -14860,7 +14872,11 @@
           <t>Accretion (Note 16)</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -15073,7 +15089,11 @@
           <t>Private placement (Note 8 and Note 10)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -16264,7 +16284,11 @@
           <t>Share repurchase</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -17128,7 +17152,11 @@
           <t>Share repurchase (Note 10(b))</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -17984,7 +18012,11 @@
           <t>Share repurchase (Note 11(c))</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -18199,7 +18231,11 @@
           <t>Purchase of equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E174" s="5" t="n">
         <v>-0.004086</v>
       </c>
@@ -18820,7 +18856,11 @@
           <t>General office expenses</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E183" s="5" t="n">
         <v>0.337772</v>
       </c>
